--- a/business_surveys/022_ai_knowledge_extraction_survey--business_surveys.xlsx
+++ b/business_surveys/022_ai_knowledge_extraction_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -971,12 +971,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'engineering_/_it',_'value':_'eng_it'}</t>
+          <t>engineering_/_it</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Engineering / IT', 'value': 'eng_it'}</t>
+          <t>Engineering / IT</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'legal_&amp;_compliance',_'value':_'legal'}</t>
+          <t>legal_&amp;_compliance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Legal &amp; Compliance', 'value': 'legal'}</t>
+          <t>Legal &amp; Compliance</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'human_resources',_'value':_'hr'}</t>
+          <t>human_resources</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Human Resources', 'value': 'hr'}</t>
+          <t>Human Resources</t>
         </is>
       </c>
     </row>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'sales_&amp;_marketing',_'value':_'sales_marketing'}</t>
+          <t>sales_&amp;_marketing</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Sales &amp; Marketing', 'value': 'sales_marketing'}</t>
+          <t>Sales &amp; Marketing</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'operations',_'value':_'operations'}</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Operations', 'value': 'operations'}</t>
+          <t>Operations</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'customer_support',_'value':_'support'}</t>
+          <t>customer_support</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Customer Support', 'value': 'support'}</t>
+          <t>Customer Support</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'internal_wiki_(notion,_confluence,_sharepoint)',_'value':_'wiki'}</t>
+          <t>internal_wiki_(notion,_confluence,_sharepoint)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Internal Wiki (Notion, Confluence, SharePoint)', 'value': 'wiki'}</t>
+          <t>Internal Wiki (Notion, Confluence, SharePoint)</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'unstructured_documents_(pdfs,_word,_ppt)',_'value':_'docs'}</t>
+          <t>unstructured_documents_(pdfs,_word,_ppt)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Unstructured Documents (PDFs, Word, PPT)', 'value': 'docs'}</t>
+          <t>Unstructured Documents (PDFs, Word, PPT)</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'email_communications',_'value':_'email'}</t>
+          <t>email_communications</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Email Communications', 'value': 'email'}</t>
+          <t>Email Communications</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'chat_history_(slack,_teams)',_'value':_'chat'}</t>
+          <t>chat_history_(slack,_teams)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Chat History (Slack, Teams)', 'value': 'chat'}</t>
+          <t>Chat History (Slack, Teams)</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'databases_(sql,_nosql)',_'value':_'databases'}</t>
+          <t>databases_(sql,_nosql)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Databases (SQL, NoSQL)', 'value': 'databases'}</t>
+          <t>Databases (SQL, NoSQL)</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'tacit_knowledge_(subject_matter_experts)',_'value':_'experts'}</t>
+          <t>tacit_knowledge_(subject_matter_experts)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Tacit Knowledge (Subject Matter Experts)', 'value': 'experts'}</t>
+          <t>Tacit Knowledge (Subject Matter Experts)</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'too_many_different_platforms',_'value':_'too_many_platforms'}</t>
+          <t>too_many_different_platforms</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Too many different platforms', 'value': 'too_many_platforms'}</t>
+          <t>Too many different platforms</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'search_results_are_irrelevant',_'value':_'irrelevant_results'}</t>
+          <t>search_results_are_irrelevant</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Search results are irrelevant', 'value': 'irrelevant_results'}</t>
+          <t>Search results are irrelevant</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'information_is_outdated',_'value':_'outdated_info'}</t>
+          <t>information_is_outdated</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Information is outdated', 'value': 'outdated_info'}</t>
+          <t>Information is outdated</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'information_is_siloed_(no_access)',_'value':_'siloed'}</t>
+          <t>information_is_siloed_(no_access)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Information is siloed (no access)', 'value': 'siloed'}</t>
+          <t>Information is siloed (no access)</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'lack_of_a_centralized_index',_'value':_'no_index'}</t>
+          <t>lack_of_a_centralized_index</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Lack of a centralized index', 'value': 'no_index'}</t>
+          <t>Lack of a centralized index</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'automatic_summarization_of_long_documents',_'value':_'summarization'}</t>
+          <t>automatic_summarization_of_long_documents</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Automatic Summarization of long documents', 'value': 'summarization'}</t>
+          <t>Automatic Summarization of long documents</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'natural_language_q&amp;a_(chat_with_your_data)',_'value':_'qa'}</t>
+          <t>natural_language_q&amp;a_(chat_with_your_data)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Natural Language Q&amp;A (Chat with your data)', 'value': 'qa'}</t>
+          <t>Natural Language Q&amp;A (Chat with your data)</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'automatic_citation_of_source_documents',_'value':_'citation'}</t>
+          <t>automatic_citation_of_source_documents</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Automatic Citation of source documents', 'value': 'citation'}</t>
+          <t>Automatic Citation of source documents</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'anomaly/conflict_detection_in_info',_'value':_'anomaly_detection'}</t>
+          <t>anomaly/conflict_detection_in_info</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Anomaly/Conflict Detection in info', 'value': 'anomaly_detection'}</t>
+          <t>Anomaly/Conflict Detection in info</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'sentiment_analysis_across_knowledge_base',_'value':_'sentiment'}</t>
+          <t>sentiment_analysis_across_knowledge_base</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Sentiment Analysis across knowledge base', 'value': 'sentiment'}</t>
+          <t>Sentiment Analysis across knowledge base</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'public_/_low_sensitivity',_'value':_'low'}</t>
+          <t>public_/_low_sensitivity</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Public / Low Sensitivity', 'value': 'low'}</t>
+          <t>Public / Low Sensitivity</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'internal_/_proprietary',_'value':_'internal'}</t>
+          <t>internal_/_proprietary</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Internal / Proprietary', 'value': 'internal'}</t>
+          <t>Internal / Proprietary</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'confidential_/_pii_included',_'value':_'confidential'}</t>
+          <t>confidential_/_pii_included</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Confidential / PII Included', 'value': 'confidential'}</t>
+          <t>Confidential / PII Included</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'highly_restricted_/_regulated_(e.g.,_hipaa/gdpr)',_'value':_'restricted'}</t>
+          <t>highly_restricted_/_regulated_(e.g.,_hipaa/gdpr)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Highly Restricted / Regulated (e.g., HIPAA/GDPR)', 'value': 'restricted'}</t>
+          <t>Highly Restricted / Regulated (e.g., HIPAA/GDPR)</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_"accuracy_/_'hallucinations'",_'value':_'accuracy'}</t>
+          <t>accuracy_/_'hallucinations'</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': "Accuracy / 'Hallucinations'", 'value': 'accuracy'}</t>
+          <t>Accuracy / 'Hallucinations'</t>
         </is>
       </c>
     </row>
@@ -1430,12 +1430,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'data_security_/_leaks',_'value':_'security'}</t>
+          <t>data_security_/_leaks</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Data Security / Leaks', 'value': 'security'}</t>
+          <t>Data Security / Leaks</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'loss_of_context',_'value':_'context_loss'}</t>
+          <t>loss_of_context</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Loss of Context', 'value': 'context_loss'}</t>
+          <t>Loss of Context</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'complexity_of_setup',_'value':_'complexity'}</t>
+          <t>complexity_of_setup</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Complexity of setup', 'value': 'complexity'}</t>
+          <t>Complexity of setup</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'maybe_(send_more_info)',_'value':_'maybe'}</t>
+          <t>maybe_(send_more_info)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Maybe (Send more info)', 'value': 'maybe'}</t>
+          <t>Maybe (Send more info)</t>
         </is>
       </c>
     </row>
